--- a/styleTable.xlsx
+++ b/styleTable.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>|</t>
   </si>
@@ -399,6 +399,72 @@
   </si>
   <si>
     <t>попооп</t>
+  </si>
+  <si>
+    <t>16.10.25</t>
+  </si>
+  <si>
+    <t>17.10.25</t>
+  </si>
+  <si>
+    <t>18.10.25</t>
+  </si>
+  <si>
+    <t>пиблс</t>
+  </si>
+  <si>
+    <t>+79054763212</t>
+  </si>
+  <si>
+    <t>клинмайбели</t>
+  </si>
+  <si>
+    <t>аооп</t>
+  </si>
+  <si>
+    <t>соао</t>
+  </si>
+  <si>
+    <t>пооп</t>
+  </si>
+  <si>
+    <t>Любит Максемо</t>
+  </si>
+  <si>
+    <t>я тебя люблю кошечка</t>
+  </si>
+  <si>
+    <t>моом</t>
+  </si>
+  <si>
+    <t>пола</t>
+  </si>
+  <si>
+    <t>попо</t>
+  </si>
+  <si>
+    <t>ата</t>
+  </si>
+  <si>
+    <t>ио</t>
+  </si>
+  <si>
+    <t>по</t>
+  </si>
+  <si>
+    <t>рои</t>
+  </si>
+  <si>
+    <t>мом</t>
+  </si>
+  <si>
+    <t>молм</t>
+  </si>
+  <si>
+    <t>мтст</t>
+  </si>
+  <si>
+    <t>мллм</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1062,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="18.75" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>2</v>
@@ -1240,7 +1306,7 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="25" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>2</v>
@@ -1470,7 +1536,7 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="23" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>2</v>
@@ -1700,7 +1766,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="23" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>2</v>
@@ -1752,10 +1818,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>10</v>
@@ -1798,10 +1864,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>10</v>
@@ -1844,10 +1910,10 @@
         <v>10</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>10</v>
@@ -1890,10 +1956,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>10</v>
@@ -1930,7 +1996,7 @@
     </row>
     <row r="21" spans="1:32">
       <c r="A21" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>2</v>
@@ -1988,7 +2054,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>10</v>
@@ -2034,7 +2100,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>10</v>
@@ -2080,7 +2146,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>10</v>
@@ -2126,7 +2192,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>10</v>
@@ -2160,7 +2226,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="A26" s="25" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>2</v>
@@ -2209,13 +2275,13 @@
         <v>10</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>10</v>
@@ -2255,13 +2321,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>10</v>
@@ -2301,13 +2367,13 @@
         <v>10</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>10</v>
@@ -2347,13 +2413,13 @@
         <v>10</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>10</v>
@@ -2390,7 +2456,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="25" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>2</v>
@@ -2439,16 +2505,16 @@
         <v>10</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>10</v>
@@ -2485,16 +2551,16 @@
         <v>10</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>10</v>
@@ -2536,16 +2602,16 @@
         <v>10</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>10</v>
@@ -2587,16 +2653,16 @@
         <v>10</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>10</v>
@@ -2635,7 +2701,7 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="25" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>2</v>
@@ -2692,13 +2758,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>10</v>
@@ -2707,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>10</v>
@@ -2743,13 +2809,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>10</v>
@@ -2758,7 +2824,7 @@
         <v>10</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>10</v>
@@ -2794,13 +2860,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>10</v>
@@ -2809,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>10</v>
@@ -2845,13 +2911,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>10</v>
@@ -2860,7 +2926,7 @@
         <v>10</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I40" s="37" t="s">
         <v>10</v>
@@ -2890,7 +2956,7 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="25" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>2</v>
@@ -2947,10 +3013,10 @@
         <v>10</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>10</v>
@@ -2998,10 +3064,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>10</v>
@@ -3049,10 +3115,10 @@
         <v>10</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>10</v>
@@ -3100,10 +3166,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>10</v>
@@ -3145,7 +3211,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="25" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="B46" s="42" t="s">
         <v>2</v>
@@ -3199,10 +3265,10 @@
         <v>10</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>10</v>
@@ -3211,7 +3277,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>10</v>
@@ -3250,10 +3316,10 @@
         <v>10</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D48" s="37" t="s">
         <v>10</v>
@@ -3262,7 +3328,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="G48" s="37" t="s">
         <v>10</v>
@@ -3301,10 +3367,10 @@
         <v>10</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="D49" s="37" t="s">
         <v>10</v>
@@ -3313,7 +3379,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="G49" s="37" t="s">
         <v>10</v>
@@ -3352,10 +3418,10 @@
         <v>10</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="D50" s="37" t="s">
         <v>10</v>
@@ -3364,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="G50" s="37" t="s">
         <v>10</v>
@@ -3400,7 +3466,7 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="25" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B51" s="42" t="s">
         <v>2</v>
@@ -3435,28 +3501,28 @@
         <v>10</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="J52" t="s">
         <v>0</v>
@@ -3467,28 +3533,28 @@
         <v>10</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="J53" t="s">
         <v>0</v>
@@ -3499,28 +3565,28 @@
         <v>10</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="J54" t="s">
         <v>0</v>
@@ -3531,28 +3597,28 @@
         <v>10</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="J55" t="s">
         <v>0</v>
@@ -3560,7 +3626,7 @@
     </row>
     <row r="56" spans="1:32">
       <c r="A56" s="25" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>2</v>
@@ -3720,7 +3786,7 @@
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="25" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>2</v>
@@ -3761,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>10</v>
@@ -3773,7 +3839,7 @@
         <v>10</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>10</v>
@@ -3793,7 +3859,7 @@
         <v>10</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>10</v>
@@ -3805,7 +3871,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I63" s="37" t="s">
         <v>10</v>
@@ -3825,7 +3891,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>10</v>
@@ -3837,7 +3903,7 @@
         <v>10</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="I64" s="37" t="s">
         <v>10</v>
@@ -3857,7 +3923,7 @@
         <v>10</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>10</v>
@@ -3869,7 +3935,7 @@
         <v>10</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>10</v>
@@ -3880,7 +3946,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="25" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="B66" s="42" t="s">
         <v>2</v>
@@ -4040,7 +4106,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="25" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="B71" s="42" t="s">
         <v>2</v>
@@ -4087,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>10</v>
@@ -4119,7 +4185,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G73" s="37" t="s">
         <v>10</v>
@@ -4151,7 +4217,7 @@
         <v>10</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>10</v>
@@ -4183,7 +4249,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G75" s="37" t="s">
         <v>10</v>
@@ -4200,7 +4266,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="25" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B76" s="42" t="s">
         <v>2</v>
@@ -4241,7 +4307,7 @@
         <v>10</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>10</v>
@@ -4250,7 +4316,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>10</v>
@@ -4273,7 +4339,7 @@
         <v>10</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>10</v>
@@ -4282,7 +4348,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H78" s="37" t="s">
         <v>10</v>
@@ -4305,7 +4371,7 @@
         <v>10</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>10</v>
@@ -4314,7 +4380,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="H79" s="37" t="s">
         <v>10</v>
@@ -4337,7 +4403,7 @@
         <v>10</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>10</v>
@@ -4346,7 +4412,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="H80" s="37" t="s">
         <v>10</v>
@@ -4360,7 +4426,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B81" s="42" t="s">
         <v>2</v>
@@ -4520,7 +4586,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="25" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B86" s="42" t="s">
         <v>2</v>
@@ -4680,7 +4746,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="25" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B91" s="42" t="s">
         <v>2</v>
@@ -4840,7 +4906,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B96" s="42" t="s">
         <v>2</v>
@@ -4884,7 +4950,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>10</v>
@@ -4916,7 +4982,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>10</v>
@@ -4948,7 +5014,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>10</v>
@@ -4980,7 +5046,7 @@
         <v>10</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>10</v>
@@ -5000,7 +5066,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B101" s="42" t="s">
         <v>2</v>
@@ -5044,7 +5110,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>10</v>
@@ -5076,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>10</v>
@@ -5108,7 +5174,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>10</v>
@@ -5140,7 +5206,7 @@
         <v>10</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>10</v>
@@ -5160,7 +5226,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="25" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B106" s="42" t="s">
         <v>2</v>
@@ -5213,7 +5279,7 @@
         <v>10</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>10</v>
@@ -5245,7 +5311,7 @@
         <v>10</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="I108" s="37" t="s">
         <v>10</v>
@@ -5277,7 +5343,7 @@
         <v>10</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="I109" s="37" t="s">
         <v>10</v>
@@ -5309,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="I110" s="37" t="s">
         <v>10</v>
@@ -5320,7 +5386,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B111" s="42" t="s">
         <v>2</v>
@@ -5480,7 +5546,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="25" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B116" s="42" t="s">
         <v>2</v>
@@ -5640,7 +5706,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="25" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B121" s="42" t="s">
         <v>2</v>
@@ -5681,7 +5747,7 @@
         <v>10</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>10</v>
@@ -5713,7 +5779,7 @@
         <v>10</v>
       </c>
       <c r="D123" s="37" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>10</v>
@@ -5745,7 +5811,7 @@
         <v>10</v>
       </c>
       <c r="D124" s="37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>10</v>
@@ -5777,7 +5843,7 @@
         <v>10</v>
       </c>
       <c r="D125" s="37" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>10</v>
@@ -5800,7 +5866,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="25" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B126" s="42" t="s">
         <v>2</v>
@@ -5838,7 +5904,7 @@
         <v>10</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>10</v>
@@ -5870,7 +5936,7 @@
         <v>10</v>
       </c>
       <c r="C128" s="37" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="D128" s="37" t="s">
         <v>10</v>
@@ -5902,7 +5968,7 @@
         <v>10</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D129" s="37" t="s">
         <v>10</v>
@@ -5934,7 +6000,7 @@
         <v>10</v>
       </c>
       <c r="C130" s="37" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="D130" s="37" t="s">
         <v>10</v>
@@ -5960,7 +6026,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B131" s="42" t="s">
         <v>2</v>
@@ -6001,7 +6067,7 @@
         <v>10</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>10</v>
@@ -6033,7 +6099,7 @@
         <v>10</v>
       </c>
       <c r="D133" s="37" t="s">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>10</v>
@@ -6065,7 +6131,7 @@
         <v>10</v>
       </c>
       <c r="D134" s="37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>10</v>
@@ -6097,7 +6163,7 @@
         <v>10</v>
       </c>
       <c r="D135" s="37" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>10</v>
@@ -6120,7 +6186,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B136" s="42" t="s">
         <v>2</v>
@@ -6260,7 +6326,7 @@
         <v>10</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>10</v>
@@ -6280,7 +6346,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B141" s="42" t="s">
         <v>2</v>
@@ -6321,7 +6387,7 @@
         <v>10</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>10</v>
+        <v>142</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>10</v>
@@ -6353,7 +6419,7 @@
         <v>10</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>10</v>
@@ -6385,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="D144" s="37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>10</v>
@@ -6417,7 +6483,7 @@
         <v>10</v>
       </c>
       <c r="D145" s="37" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>10</v>
@@ -6440,7 +6506,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B146" s="42" t="s">
         <v>2</v>
@@ -6493,7 +6559,7 @@
         <v>10</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="I147" s="9" t="s">
         <v>10</v>
@@ -6525,7 +6591,7 @@
         <v>10</v>
       </c>
       <c r="H148" s="37" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="I148" s="37" t="s">
         <v>10</v>
@@ -6557,7 +6623,7 @@
         <v>10</v>
       </c>
       <c r="H149" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I149" s="37" t="s">
         <v>10</v>
@@ -6589,7 +6655,7 @@
         <v>10</v>
       </c>
       <c r="H150" s="37" t="s">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="I150" s="37" t="s">
         <v>10</v>
@@ -6600,7 +6666,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B151" s="42" t="s">
         <v>2</v>

--- a/styleTable.xlsx
+++ b/styleTable.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>|</t>
   </si>
@@ -465,6 +465,108 @@
   </si>
   <si>
     <t>мллм</t>
+  </si>
+  <si>
+    <t>01.10.25</t>
+  </si>
+  <si>
+    <t>Елизавета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Соня </t>
+  </si>
+  <si>
+    <t>Анастасия</t>
+  </si>
+  <si>
+    <t>Фирсова</t>
+  </si>
+  <si>
+    <t>Кузнецова</t>
+  </si>
+  <si>
+    <t>Войткевич</t>
+  </si>
+  <si>
+    <t>54656</t>
+  </si>
+  <si>
+    <t>6574565</t>
+  </si>
+  <si>
+    <t>546565</t>
+  </si>
+  <si>
+    <t>3129792</t>
+  </si>
+  <si>
+    <t>3867655</t>
+  </si>
+  <si>
+    <t>53535</t>
+  </si>
+  <si>
+    <t>vbnb</t>
+  </si>
+  <si>
+    <t>dfgfsdg</t>
+  </si>
+  <si>
+    <t>bgdgdfg</t>
+  </si>
+  <si>
+    <t>02.10.25</t>
+  </si>
+  <si>
+    <t>03.10.25</t>
+  </si>
+  <si>
+    <t>04.10.25</t>
+  </si>
+  <si>
+    <t>05.10.25</t>
+  </si>
+  <si>
+    <t>06.10.25</t>
+  </si>
+  <si>
+    <t>07.10.25</t>
+  </si>
+  <si>
+    <t>08.10.25</t>
+  </si>
+  <si>
+    <t>09.10.25</t>
+  </si>
+  <si>
+    <t>10.10.25</t>
+  </si>
+  <si>
+    <t>11.10.25</t>
+  </si>
+  <si>
+    <t>12.10.25</t>
+  </si>
+  <si>
+    <t>13.10.25</t>
+  </si>
+  <si>
+    <t>14.10.25</t>
+  </si>
+  <si>
+    <t>15.10.25</t>
+  </si>
+  <si>
+    <t>Илья</t>
+  </si>
+  <si>
+    <t>Новиков</t>
+  </si>
+  <si>
+    <t>89157450308</t>
+  </si>
+  <si>
+    <t>Пескоструй рамы</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1164,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="18.75" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>2</v>
@@ -1117,28 +1219,28 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -1165,28 +1267,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="J3" t="s">
         <v>0</v>
@@ -1213,28 +1315,28 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="J4" t="s">
         <v>0</v>
@@ -1261,28 +1363,28 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="J5" t="s">
         <v>0</v>
@@ -1306,7 +1408,7 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="25" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>2</v>
@@ -1361,7 +1463,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>10</v>
@@ -1370,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="H7" s="37" t="s">
         <v>10</v>
@@ -1407,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>10</v>
@@ -1416,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>10</v>
@@ -1453,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="E9" s="38" t="s">
         <v>10</v>
@@ -1462,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="H9" s="38" t="s">
         <v>10</v>
@@ -1499,7 +1601,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>10</v>
@@ -1508,7 +1610,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>10</v>
@@ -1536,7 +1638,7 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="23" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>2</v>
@@ -1766,7 +1868,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="23" t="s">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>2</v>
@@ -1815,28 +1917,28 @@
         <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="J17" t="s">
         <v>0</v>
@@ -1861,28 +1963,28 @@
         <v>10</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="J18" t="s">
         <v>0</v>
@@ -1907,28 +2009,28 @@
         <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="J19" t="s">
         <v>0</v>
@@ -1953,28 +2055,28 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="J20" t="s">
         <v>0</v>
@@ -1996,7 +2098,7 @@
     </row>
     <row r="21" spans="1:32">
       <c r="A21" s="25" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>2</v>
@@ -2054,10 +2156,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>10</v>
@@ -2100,10 +2202,10 @@
         <v>10</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>10</v>
@@ -2146,10 +2248,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>10</v>
@@ -2192,10 +2294,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>10</v>
@@ -2226,7 +2328,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="A26" s="25" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>2</v>
@@ -2456,7 +2558,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="25" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>2</v>
@@ -2701,7 +2803,7 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="25" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>2</v>
@@ -2956,7 +3058,7 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="25" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>2</v>
@@ -3013,7 +3115,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>10</v>
@@ -3064,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D43" s="37" t="s">
         <v>10</v>
@@ -3115,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D44" s="37" t="s">
         <v>10</v>
@@ -3166,7 +3268,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>10</v>
@@ -3211,7 +3313,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="25" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="B46" s="42" t="s">
         <v>2</v>
@@ -3466,7 +3568,7 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="25" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="B51" s="42" t="s">
         <v>2</v>
@@ -3501,7 +3603,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>10</v>
@@ -3533,7 +3635,7 @@
         <v>10</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C53" s="37" t="s">
         <v>10</v>
@@ -3565,7 +3667,7 @@
         <v>10</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C54" s="37" t="s">
         <v>10</v>
@@ -3597,7 +3699,7 @@
         <v>10</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C55" s="37" t="s">
         <v>10</v>
@@ -3626,7 +3728,7 @@
     </row>
     <row r="56" spans="1:32">
       <c r="A56" s="25" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>2</v>
@@ -3786,7 +3888,7 @@
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="25" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>2</v>
@@ -3827,7 +3929,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>10</v>
@@ -3839,7 +3941,7 @@
         <v>10</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>10</v>
@@ -3859,7 +3961,7 @@
         <v>10</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>10</v>
@@ -3871,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I63" s="37" t="s">
         <v>10</v>
@@ -3891,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>10</v>
@@ -3903,7 +4005,7 @@
         <v>10</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="I64" s="37" t="s">
         <v>10</v>
@@ -3923,7 +4025,7 @@
         <v>10</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>10</v>
@@ -3935,7 +4037,7 @@
         <v>10</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>10</v>
@@ -3946,7 +4048,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="25" t="s">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="B66" s="42" t="s">
         <v>2</v>
@@ -4106,7 +4208,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="25" t="s">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="B71" s="42" t="s">
         <v>2</v>
@@ -4153,7 +4255,7 @@
         <v>10</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>10</v>
@@ -4185,7 +4287,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="G73" s="37" t="s">
         <v>10</v>
@@ -4217,7 +4319,7 @@
         <v>10</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>10</v>
@@ -4249,7 +4351,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="G75" s="37" t="s">
         <v>10</v>
@@ -4266,7 +4368,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="25" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="B76" s="42" t="s">
         <v>2</v>
@@ -4307,7 +4409,7 @@
         <v>10</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>10</v>
@@ -4316,7 +4418,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>10</v>
@@ -4339,7 +4441,7 @@
         <v>10</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>10</v>
@@ -4348,7 +4450,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H78" s="37" t="s">
         <v>10</v>
@@ -4371,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>10</v>
@@ -4380,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="H79" s="37" t="s">
         <v>10</v>
@@ -4403,7 +4505,7 @@
         <v>10</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>10</v>
@@ -4412,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H80" s="37" t="s">
         <v>10</v>
@@ -4426,7 +4528,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="25" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B81" s="42" t="s">
         <v>2</v>
@@ -4586,7 +4688,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="25" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B86" s="42" t="s">
         <v>2</v>
@@ -4746,7 +4848,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="25" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="B91" s="42" t="s">
         <v>2</v>
@@ -4787,7 +4889,7 @@
         <v>10</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>10</v>
@@ -4819,7 +4921,7 @@
         <v>10</v>
       </c>
       <c r="D93" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>10</v>
@@ -4851,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>10</v>
@@ -4883,7 +4985,7 @@
         <v>10</v>
       </c>
       <c r="D95" s="37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>10</v>
@@ -4906,7 +5008,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="25" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="B96" s="42" t="s">
         <v>2</v>
@@ -4950,7 +5052,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>10</v>
@@ -4982,7 +5084,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>10</v>
@@ -5014,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>10</v>
@@ -5046,7 +5148,7 @@
         <v>10</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>10</v>
@@ -5066,7 +5168,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="25" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="B101" s="42" t="s">
         <v>2</v>
@@ -5226,7 +5328,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="25" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="B106" s="42" t="s">
         <v>2</v>
@@ -5279,7 +5381,7 @@
         <v>10</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>10</v>
@@ -5311,7 +5413,7 @@
         <v>10</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="I108" s="37" t="s">
         <v>10</v>
@@ -5343,7 +5445,7 @@
         <v>10</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="I109" s="37" t="s">
         <v>10</v>
@@ -5375,7 +5477,7 @@
         <v>10</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="I110" s="37" t="s">
         <v>10</v>
@@ -5386,7 +5488,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="25" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="B111" s="42" t="s">
         <v>2</v>
@@ -5546,7 +5648,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="25" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="B116" s="42" t="s">
         <v>2</v>
@@ -5584,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>10</v>
@@ -5616,7 +5718,7 @@
         <v>10</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D118" s="37" t="s">
         <v>10</v>
@@ -5648,7 +5750,7 @@
         <v>10</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D119" s="37" t="s">
         <v>10</v>
@@ -5680,7 +5782,7 @@
         <v>10</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D120" s="37" t="s">
         <v>10</v>
@@ -5706,7 +5808,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="25" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="B121" s="42" t="s">
         <v>2</v>
@@ -5747,7 +5849,7 @@
         <v>10</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>10</v>
@@ -5779,7 +5881,7 @@
         <v>10</v>
       </c>
       <c r="D123" s="37" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>10</v>
@@ -5811,7 +5913,7 @@
         <v>10</v>
       </c>
       <c r="D124" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>10</v>
@@ -5843,7 +5945,7 @@
         <v>10</v>
       </c>
       <c r="D125" s="37" t="s">
-        <v>135</v>
+        <v>10</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>10</v>
@@ -5866,7 +5968,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="25" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="B126" s="42" t="s">
         <v>2</v>
@@ -5901,10 +6003,10 @@
         <v>10</v>
       </c>
       <c r="B127" s="37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>10</v>
@@ -5933,10 +6035,10 @@
         <v>10</v>
       </c>
       <c r="B128" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C128" s="37" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D128" s="37" t="s">
         <v>10</v>
@@ -5965,10 +6067,10 @@
         <v>10</v>
       </c>
       <c r="B129" s="37" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D129" s="37" t="s">
         <v>10</v>
@@ -5997,10 +6099,10 @@
         <v>10</v>
       </c>
       <c r="B130" s="37" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C130" s="37" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="D130" s="37" t="s">
         <v>10</v>
@@ -6026,7 +6128,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="25" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="B131" s="42" t="s">
         <v>2</v>
@@ -6067,7 +6169,7 @@
         <v>10</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>10</v>
@@ -6099,7 +6201,7 @@
         <v>10</v>
       </c>
       <c r="D133" s="37" t="s">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>10</v>
@@ -6131,7 +6233,7 @@
         <v>10</v>
       </c>
       <c r="D134" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>10</v>
@@ -6163,7 +6265,7 @@
         <v>10</v>
       </c>
       <c r="D135" s="37" t="s">
-        <v>140</v>
+        <v>10</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>10</v>
@@ -6186,7 +6288,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="25" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="B136" s="42" t="s">
         <v>2</v>
@@ -6227,7 +6329,7 @@
         <v>10</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>10</v>
@@ -6239,7 +6341,7 @@
         <v>10</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="I137" s="9" t="s">
         <v>10</v>
@@ -6259,7 +6361,7 @@
         <v>10</v>
       </c>
       <c r="D138" s="37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>10</v>
@@ -6271,7 +6373,7 @@
         <v>10</v>
       </c>
       <c r="H138" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I138" s="37" t="s">
         <v>10</v>
@@ -6291,7 +6393,7 @@
         <v>10</v>
       </c>
       <c r="D139" s="37" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>10</v>
@@ -6303,7 +6405,7 @@
         <v>10</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="I139" s="37" t="s">
         <v>10</v>
@@ -6323,10 +6425,10 @@
         <v>10</v>
       </c>
       <c r="D140" s="37" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>10</v>
@@ -6335,7 +6437,7 @@
         <v>10</v>
       </c>
       <c r="H140" s="37" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I140" s="37" t="s">
         <v>10</v>
@@ -6346,7 +6448,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="25" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="B141" s="42" t="s">
         <v>2</v>
@@ -6387,7 +6489,7 @@
         <v>10</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>10</v>
@@ -6419,7 +6521,7 @@
         <v>10</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>10</v>
@@ -6451,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="D144" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>10</v>
@@ -6483,7 +6585,7 @@
         <v>10</v>
       </c>
       <c r="D145" s="37" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>10</v>
@@ -6506,7 +6608,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="25" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="B146" s="42" t="s">
         <v>2</v>
@@ -6553,7 +6655,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G147" s="9" t="s">
         <v>10</v>
@@ -6585,7 +6687,7 @@
         <v>10</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G148" s="37" t="s">
         <v>10</v>
@@ -6617,7 +6719,7 @@
         <v>10</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="G149" s="37" t="s">
         <v>10</v>
@@ -6649,7 +6751,7 @@
         <v>10</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G150" s="37" t="s">
         <v>10</v>
@@ -6666,7 +6768,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="25" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="B151" s="42" t="s">
         <v>2</v>
@@ -6707,16 +6809,16 @@
         <v>10</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H152" s="9" t="s">
         <v>10</v>
@@ -6739,16 +6841,16 @@
         <v>10</v>
       </c>
       <c r="D153" s="37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="G153" s="37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H153" s="37" t="s">
         <v>10</v>
@@ -6771,16 +6873,16 @@
         <v>10</v>
       </c>
       <c r="D154" s="37" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="G154" s="37" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="H154" s="37" t="s">
         <v>10</v>
@@ -6803,16 +6905,16 @@
         <v>10</v>
       </c>
       <c r="D155" s="37" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="G155" s="37" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="H155" s="37" t="s">
         <v>10</v>

--- a/styleTable.xlsx
+++ b/styleTable.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>|</t>
   </si>
@@ -567,6 +567,18 @@
   </si>
   <si>
     <t>Пескоструй рамы</t>
+  </si>
+  <si>
+    <t>сос</t>
+  </si>
+  <si>
+    <t>мо</t>
+  </si>
+  <si>
+    <t>893746464646</t>
+  </si>
+  <si>
+    <t>г</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>10</v>
@@ -3424,7 +3436,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>10</v>
@@ -3475,7 +3487,7 @@
         <v>10</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>10</v>
+        <v>181</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>10</v>
@@ -3526,7 +3538,7 @@
         <v>10</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>10</v>
@@ -6489,7 +6501,7 @@
         <v>10</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>10</v>
@@ -6521,7 +6533,7 @@
         <v>10</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>10</v>
@@ -6553,7 +6565,7 @@
         <v>10</v>
       </c>
       <c r="D144" s="37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>10</v>
@@ -6585,7 +6597,7 @@
         <v>10</v>
       </c>
       <c r="D145" s="37" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>10</v>

--- a/styleTable.xlsx
+++ b/styleTable.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t>|</t>
   </si>
@@ -579,6 +579,93 @@
   </si>
   <si>
     <t>г</t>
+  </si>
+  <si>
+    <t>оп</t>
+  </si>
+  <si>
+    <t>о</t>
+  </si>
+  <si>
+    <t>та</t>
+  </si>
+  <si>
+    <t>мт</t>
+  </si>
+  <si>
+    <t>со</t>
+  </si>
+  <si>
+    <t>л</t>
+  </si>
+  <si>
+    <t>пл</t>
+  </si>
+  <si>
+    <t>ао</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>89158474747</t>
+  </si>
+  <si>
+    <t>891574637474</t>
+  </si>
+  <si>
+    <t>89154747474</t>
+  </si>
+  <si>
+    <t>87373737383</t>
+  </si>
+  <si>
+    <t>891548448474</t>
+  </si>
+  <si>
+    <t>891648447474</t>
+  </si>
+  <si>
+    <t>891583748438</t>
+  </si>
+  <si>
+    <t>п</t>
+  </si>
+  <si>
+    <t>21.11.25</t>
+  </si>
+  <si>
+    <t>22.11.25</t>
+  </si>
+  <si>
+    <t>23.11.25</t>
+  </si>
+  <si>
+    <t>24.11.25</t>
+  </si>
+  <si>
+    <t>25.11.25</t>
+  </si>
+  <si>
+    <t>26.11.25</t>
+  </si>
+  <si>
+    <t>27.11.25</t>
+  </si>
+  <si>
+    <t>28.11.25</t>
+  </si>
+  <si>
+    <t>29.11.25</t>
+  </si>
+  <si>
+    <t>30.11.25</t>
+  </si>
+  <si>
+    <t>01.12.25</t>
+  </si>
+  <si>
+    <t>02.12.25</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1263,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="18.75" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>2</v>
@@ -1231,28 +1318,28 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -1279,28 +1366,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
         <v>0</v>
@@ -1327,28 +1414,28 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
         <v>0</v>
@@ -1375,28 +1462,28 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
         <v>0</v>
@@ -1420,7 +1507,7 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="25" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>2</v>
@@ -1475,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>10</v>
@@ -1484,7 +1571,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="H7" s="37" t="s">
         <v>10</v>
@@ -1521,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>10</v>
@@ -1530,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>10</v>
@@ -1567,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E9" s="38" t="s">
         <v>10</v>
@@ -1576,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="H9" s="38" t="s">
         <v>10</v>
@@ -1613,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>10</v>
@@ -1622,7 +1709,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>10</v>
@@ -1650,7 +1737,7 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="23" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>2</v>
@@ -1880,7 +1967,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="23" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>2</v>
@@ -1929,28 +2016,28 @@
         <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="J17" t="s">
         <v>0</v>
@@ -1975,28 +2062,28 @@
         <v>10</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="J18" t="s">
         <v>0</v>
@@ -2021,28 +2108,28 @@
         <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="J19" t="s">
         <v>0</v>
@@ -2067,28 +2154,28 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="J20" t="s">
         <v>0</v>
@@ -2110,7 +2197,7 @@
     </row>
     <row r="21" spans="1:32">
       <c r="A21" s="25" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>2</v>
@@ -2168,10 +2255,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>10</v>
@@ -2214,10 +2301,10 @@
         <v>10</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>10</v>
@@ -2260,10 +2347,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>10</v>
@@ -2306,10 +2393,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>10</v>
@@ -2340,7 +2427,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="A26" s="25" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>2</v>
@@ -2570,7 +2657,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="25" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>2</v>
@@ -2815,7 +2902,7 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="25" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>2</v>
@@ -3070,7 +3157,7 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="25" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>2</v>
@@ -3325,7 +3412,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="25" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="B46" s="42" t="s">
         <v>2</v>
@@ -3385,7 +3472,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>10</v>
@@ -3436,7 +3523,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>10</v>
@@ -3487,7 +3574,7 @@
         <v>10</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>181</v>
+        <v>10</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>10</v>
@@ -3538,7 +3625,7 @@
         <v>10</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>182</v>
+        <v>10</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>10</v>
@@ -3580,7 +3667,7 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="25" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="B51" s="42" t="s">
         <v>2</v>
@@ -3740,7 +3827,7 @@
     </row>
     <row r="56" spans="1:32">
       <c r="A56" s="25" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>2</v>
@@ -3900,7 +3987,7 @@
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="25" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>2</v>
@@ -4060,7 +4147,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="25" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B66" s="42" t="s">
         <v>2</v>
@@ -4220,7 +4307,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="25" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="B71" s="42" t="s">
         <v>2</v>
@@ -4380,7 +4467,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="25" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B76" s="42" t="s">
         <v>2</v>
@@ -4540,7 +4627,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="25" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B81" s="42" t="s">
         <v>2</v>
@@ -4700,7 +4787,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B86" s="42" t="s">
         <v>2</v>
@@ -4860,7 +4947,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="25" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="B91" s="42" t="s">
         <v>2</v>
@@ -4901,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>10</v>
@@ -4933,7 +5020,7 @@
         <v>10</v>
       </c>
       <c r="D93" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>10</v>
@@ -4965,7 +5052,7 @@
         <v>10</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>10</v>
@@ -4997,7 +5084,7 @@
         <v>10</v>
       </c>
       <c r="D95" s="37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>10</v>
@@ -5020,7 +5107,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="25" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="B96" s="42" t="s">
         <v>2</v>
@@ -5180,7 +5267,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="25" t="s">
-        <v>16</v>
+        <v>201</v>
       </c>
       <c r="B101" s="42" t="s">
         <v>2</v>
@@ -5340,7 +5427,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="25" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="B106" s="42" t="s">
         <v>2</v>
@@ -5500,7 +5587,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="25" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="B111" s="42" t="s">
         <v>2</v>
@@ -5660,7 +5747,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="25" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="B116" s="42" t="s">
         <v>2</v>
@@ -5698,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>10</v>
@@ -5730,7 +5817,7 @@
         <v>10</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D118" s="37" t="s">
         <v>10</v>
@@ -5762,7 +5849,7 @@
         <v>10</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D119" s="37" t="s">
         <v>10</v>
@@ -5794,7 +5881,7 @@
         <v>10</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D120" s="37" t="s">
         <v>10</v>
@@ -5820,7 +5907,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="25" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="B121" s="42" t="s">
         <v>2</v>
@@ -5980,7 +6067,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="25" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="B126" s="42" t="s">
         <v>2</v>
@@ -6015,7 +6102,7 @@
         <v>10</v>
       </c>
       <c r="B127" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C127" s="9" t="s">
         <v>10</v>
@@ -6047,7 +6134,7 @@
         <v>10</v>
       </c>
       <c r="B128" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C128" s="37" t="s">
         <v>10</v>
@@ -6079,7 +6166,7 @@
         <v>10</v>
       </c>
       <c r="B129" s="37" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C129" s="37" t="s">
         <v>10</v>
@@ -6111,7 +6198,7 @@
         <v>10</v>
       </c>
       <c r="B130" s="37" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C130" s="37" t="s">
         <v>10</v>
@@ -6140,7 +6227,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="25" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="B131" s="42" t="s">
         <v>2</v>
@@ -6300,7 +6387,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="25" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="B136" s="42" t="s">
         <v>2</v>
@@ -6341,7 +6428,7 @@
         <v>10</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>10</v>
@@ -6353,7 +6440,7 @@
         <v>10</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I137" s="9" t="s">
         <v>10</v>
@@ -6373,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="D138" s="37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>10</v>
@@ -6385,7 +6472,7 @@
         <v>10</v>
       </c>
       <c r="H138" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I138" s="37" t="s">
         <v>10</v>
@@ -6405,7 +6492,7 @@
         <v>10</v>
       </c>
       <c r="D139" s="37" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>10</v>
@@ -6417,7 +6504,7 @@
         <v>10</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="I139" s="37" t="s">
         <v>10</v>
@@ -6437,7 +6524,7 @@
         <v>10</v>
       </c>
       <c r="D140" s="37" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>10</v>
@@ -6449,7 +6536,7 @@
         <v>10</v>
       </c>
       <c r="H140" s="37" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I140" s="37" t="s">
         <v>10</v>
@@ -6460,7 +6547,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="25" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="B141" s="42" t="s">
         <v>2</v>
@@ -6501,7 +6588,7 @@
         <v>10</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>10</v>
@@ -6533,7 +6620,7 @@
         <v>10</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>10</v>
@@ -6565,7 +6652,7 @@
         <v>10</v>
       </c>
       <c r="D144" s="37" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>10</v>
@@ -6597,7 +6684,7 @@
         <v>10</v>
       </c>
       <c r="D145" s="37" t="s">
-        <v>179</v>
+        <v>10</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>10</v>
@@ -6620,7 +6707,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="25" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="B146" s="42" t="s">
         <v>2</v>
@@ -6667,7 +6754,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="G147" s="9" t="s">
         <v>10</v>
@@ -6699,7 +6786,7 @@
         <v>10</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="G148" s="37" t="s">
         <v>10</v>
@@ -6731,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="G149" s="37" t="s">
         <v>10</v>
@@ -6763,7 +6850,7 @@
         <v>10</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="G150" s="37" t="s">
         <v>10</v>
@@ -6780,7 +6867,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="25" t="s">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="B151" s="42" t="s">
         <v>2</v>
@@ -6821,16 +6908,16 @@
         <v>10</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H152" s="9" t="s">
         <v>10</v>
@@ -6853,16 +6940,16 @@
         <v>10</v>
       </c>
       <c r="D153" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="G153" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H153" s="37" t="s">
         <v>10</v>
@@ -6885,16 +6972,16 @@
         <v>10</v>
       </c>
       <c r="D154" s="37" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="G154" s="37" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="H154" s="37" t="s">
         <v>10</v>
@@ -6917,16 +7004,16 @@
         <v>10</v>
       </c>
       <c r="D155" s="37" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="G155" s="37" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H155" s="37" t="s">
         <v>10</v>

--- a/styleTable.xlsx
+++ b/styleTable.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t>|</t>
   </si>
@@ -666,6 +666,12 @@
   </si>
   <si>
     <t>02.12.25</t>
+  </si>
+  <si>
+    <t>03.12.25</t>
+  </si>
+  <si>
+    <t>04.12.25</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1269,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="18.75" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>2</v>
@@ -1507,7 +1513,7 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>2</v>
@@ -1737,7 +1743,7 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>2</v>
@@ -1967,7 +1973,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>2</v>
@@ -2197,7 +2203,7 @@
     </row>
     <row r="21" spans="1:32">
       <c r="A21" s="25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>2</v>
@@ -2427,7 +2433,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="A26" s="25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>2</v>
@@ -2657,7 +2663,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="A31" s="25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>2</v>
@@ -2902,7 +2908,7 @@
     </row>
     <row r="36" spans="1:32">
       <c r="A36" s="25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>2</v>
@@ -3157,7 +3163,7 @@
     </row>
     <row r="41" spans="1:32">
       <c r="A41" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B41" s="42" t="s">
         <v>2</v>
@@ -3412,7 +3418,7 @@
     </row>
     <row r="46" spans="1:32">
       <c r="A46" s="25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B46" s="42" t="s">
         <v>2</v>
@@ -3667,7 +3673,7 @@
     </row>
     <row r="51" spans="1:32">
       <c r="A51" s="25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B51" s="42" t="s">
         <v>2</v>
@@ -3827,7 +3833,7 @@
     </row>
     <row r="56" spans="1:32">
       <c r="A56" s="25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>2</v>
@@ -3987,7 +3993,7 @@
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>2</v>
@@ -4147,7 +4153,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B66" s="42" t="s">
         <v>2</v>
@@ -4307,7 +4313,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B71" s="42" t="s">
         <v>2</v>
@@ -4467,7 +4473,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B76" s="42" t="s">
         <v>2</v>
@@ -4627,7 +4633,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B81" s="42" t="s">
         <v>2</v>
@@ -4787,7 +4793,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="25" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="B86" s="42" t="s">
         <v>2</v>
@@ -4947,7 +4953,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="25" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="B91" s="42" t="s">
         <v>2</v>
@@ -5107,7 +5113,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="25" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B96" s="42" t="s">
         <v>2</v>
@@ -5267,7 +5273,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="25" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B101" s="42" t="s">
         <v>2</v>
@@ -5427,7 +5433,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="25" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B106" s="42" t="s">
         <v>2</v>
@@ -5587,7 +5593,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="25" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B111" s="42" t="s">
         <v>2</v>
@@ -5747,7 +5753,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="25" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B116" s="42" t="s">
         <v>2</v>
@@ -5907,7 +5913,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="25" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B121" s="42" t="s">
         <v>2</v>
@@ -6067,7 +6073,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="25" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B126" s="42" t="s">
         <v>2</v>
@@ -6227,7 +6233,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B131" s="42" t="s">
         <v>2</v>
@@ -6387,7 +6393,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B136" s="42" t="s">
         <v>2</v>
@@ -6547,7 +6553,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="25" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B141" s="42" t="s">
         <v>2</v>
@@ -6707,7 +6713,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B146" s="42" t="s">
         <v>2</v>
@@ -6867,7 +6873,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B151" s="42" t="s">
         <v>2</v>
